--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/08_it_budget_spend_value.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/08_it_budget_spend_value.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6585b174b9114238"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R2356e9c901344386"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R6c2d742d97344f1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R4a4ba3c9a48642a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Ra620c53427b642a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rf1556ae477cb4f9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tower Views" sheetId="7" r:id="R6bac2414d2ad47d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R52012319a5564aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R84b5444da23849e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rb10d4c3940e9400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R1a04ea7488554540"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R771bbc0a644c45d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R3fe7d3a26b214669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tower Views" sheetId="7" r:id="R991c05cbe5134fe4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -640,7 +640,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1568e3cf549245fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc898671c0a3b4ac4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -821,7 +821,7 @@
         <x:v>Chief Strategy Officer</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Executive Office run spend baseline (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -871,7 +871,7 @@
         <x:v>Chief Strategy Officer</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Enterprise profile and corporate priorities change / modernization budget (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -921,7 +921,7 @@
         <x:v>CMO</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for Provider Operations run spend baseline (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>Medium</x:v>
@@ -971,7 +971,7 @@
         <x:v>CMO</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile Provider / clinical operations change / modernization budget (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>Medium</x:v>
@@ -1021,7 +1021,7 @@
         <x:v>Health Plan COO</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Operations run spend baseline (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>Medium</x:v>
@@ -1071,7 +1071,7 @@
         <x:v>Health Plan COO</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Payer / claims operations change / modernization budget (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>Medium</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>VP Benefits Operations</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm Eligibility and Benefits run spend baseline (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>Medium</x:v>
@@ -1171,7 +1171,7 @@
         <x:v>VP Benefits Operations</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for Eligibility / benefits change / modernization budget (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>Medium</x:v>
@@ -1221,7 +1221,7 @@
         <x:v>VP Utilization Management</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Reconcile Prior Authorization and UM run spend baseline (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>Medium</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>VP Utilization Management</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior authorization / utilization management change / modernization budget (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>Medium</x:v>
@@ -1321,7 +1321,7 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Contact Center and Member Service run spend baseline (record 11) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>Medium</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Member experience / contact center change / modernization budget (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>Medium</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>Revenue Cycle Leader</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for Revenue Cycle Operations run spend baseline (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>Medium</x:v>
@@ -1471,7 +1471,7 @@
         <x:v>Revenue Cycle Leader</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile Revenue cycle change / modernization budget (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>Medium</x:v>
@@ -1521,7 +1521,7 @@
         <x:v>CFO</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Finance Analytics run spend baseline (record 15) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>Medium</x:v>
@@ -1571,7 +1571,7 @@
         <x:v>CFO</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Finance analytics change / modernization budget (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>Medium</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>CHRO</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm Workforce Analytics run spend baseline (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>Medium</x:v>
@@ -1671,7 +1671,7 @@
         <x:v>CHRO</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for HR / workforce analytics change / modernization budget (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>Medium</x:v>
@@ -1721,7 +1721,7 @@
         <x:v>VP Quality</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics run spend baseline (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>Medium</x:v>
@@ -1771,7 +1771,7 @@
         <x:v>VP Quality</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical quality analytics change / modernization budget (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>Medium</x:v>
@@ -1821,7 +1821,7 @@
         <x:v>VP Claims Analytics</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Claims and Payment Analytics run spend baseline (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>Medium</x:v>
@@ -1871,7 +1871,7 @@
         <x:v>VP Claims Analytics</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Claims analytics change / modernization budget (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>Medium</x:v>
@@ -1921,7 +1921,7 @@
         <x:v>VP Provider Performance</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for Provider Performance Analytics run spend baseline (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P28" t="str">
         <x:v>Medium</x:v>
@@ -1971,7 +1971,7 @@
         <x:v>VP Provider Performance</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile Provider performance analytics change / modernization budget (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P29" t="str">
         <x:v>Medium</x:v>
@@ -2021,7 +2021,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Enterprise Data Platform run spend baseline (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P30" t="str">
         <x:v>Medium</x:v>
@@ -2071,7 +2071,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Enterprise data platform / lakehouse change / modernization budget (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P31" t="str">
         <x:v>Medium</x:v>
@@ -2121,7 +2121,7 @@
         <x:v>Chief Data Officer</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm Data Governance and Data Quality run spend baseline (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P32" t="str">
         <x:v>Medium</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>Chief Data Officer</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for Data governance, quality, catalog, MDM change / modernization budget (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P33" t="str">
         <x:v>Medium</x:v>
@@ -2221,7 +2221,7 @@
         <x:v>VP Contact Center</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action run spend baseline (record 29) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P34" t="str">
         <x:v>Medium</x:v>
@@ -2271,7 +2271,7 @@
         <x:v>VP Contact Center</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Agent Assist for member service change / modernization budget (record 30) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P35" t="str">
         <x:v>Medium</x:v>
@@ -2321,7 +2321,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse run spend baseline (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P36" t="str">
         <x:v>Medium</x:v>
@@ -2371,7 +2371,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Unified clinical + claims lakehouse change / modernization budget (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P37" t="str">
         <x:v>Medium</x:v>
@@ -2421,7 +2421,7 @@
         <x:v>CIO / CFO</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline run spend baseline (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P38" t="str">
         <x:v>Medium</x:v>
@@ -2471,7 +2471,7 @@
         <x:v>CIO / CFO</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile IT budget and Tower spend baseline change / modernization budget (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P39" t="str">
         <x:v>Medium</x:v>
@@ -2521,7 +2521,7 @@
         <x:v>Chief Procurement Officer</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization run spend baseline (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P40" t="str">
         <x:v>Medium</x:v>
@@ -2571,7 +2571,7 @@
         <x:v>Chief Procurement Officer</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Vendor / contract / sourcing context change / modernization budget (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P41" t="str">
         <x:v>Medium</x:v>
@@ -2621,7 +2621,7 @@
         <x:v>CTO</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm Infrastructure and CMDB run spend baseline (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P42" t="str">
         <x:v>Medium</x:v>
@@ -2671,7 +2671,7 @@
         <x:v>CTO</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for CMDB / infrastructure / cloud inventory context change / modernization budget (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P43" t="str">
         <x:v>Medium</x:v>
@@ -2721,7 +2721,7 @@
         <x:v>VP IT Operations</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations run spend baseline (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P44" t="str">
         <x:v>Medium</x:v>
@@ -2771,7 +2771,7 @@
         <x:v>VP IT Operations</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident / problem / change operational health context change / modernization budget (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P45" t="str">
         <x:v>Medium</x:v>
@@ -2804,7 +2804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0d8a8b91f664689"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff85b336a1c1478a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2879,7 +2879,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree4b79c719e24ad0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30d50a18624a4535"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3071,7 +3071,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce01e9dc5a374cb0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11a583a580c44a9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3165,7 +3165,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc3b343f7055473c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red612f0e82644c6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3275,7 +3275,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1133f633a8341cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a5b565d82724584"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3383,7 +3383,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R002b42f3f62c4a40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f13028a765548c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>